--- a/artfynd/A 36431-2021 artfynd.xlsx
+++ b/artfynd/A 36431-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36431-2021 artfynd.xlsx
+++ b/artfynd/A 36431-2021 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79773300</v>
+        <v>97758162</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
+          <t>Sveds tallskog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447382.0620379847</v>
+        <v>447199</v>
       </c>
       <c r="R2" t="n">
-        <v>6430307.255464219</v>
+        <v>6430438</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,27 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Gustav Adolf</t>
+          <t>Habo</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:36</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,76 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
+          <t>Elinor Molinari</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
-        </is>
-      </c>
+          <t>Elinor Molinari</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80283006</v>
+        <v>79773302</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447313.4093573572</v>
+        <v>447382</v>
       </c>
       <c r="R3" t="n">
-        <v>6430374.925783207</v>
+        <v>6430307</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-05</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,58 +888,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79773302</v>
+        <v>80283006</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gustav Adolf distrikt, Fagerhult, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447382.0620379847</v>
+        <v>447313</v>
       </c>
       <c r="R4" t="n">
-        <v>6430307.255464219</v>
+        <v>6430375</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,22 +960,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2019-10-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1044,12 +1010,7 @@
         <v>89140762</v>
       </c>
       <c r="B5" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447438.1365797513</v>
+        <v>447438</v>
       </c>
       <c r="R5" t="n">
-        <v>6430372.751417764</v>
+        <v>6430373</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1075,9 @@
           <t>2020-09-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
